--- a/algorithm/data/调查数据表--模板.xlsx
+++ b/algorithm/data/调查数据表--模板.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="22280"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -721,14 +721,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1042,13 +1042,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K44"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="10.9230769230769"/>
-    <col min="2" max="2" width="25.9134615384615" customWidth="1"/>
-    <col min="3" max="4" width="14.6346153846154" customWidth="1"/>
-    <col min="5" max="5" width="14.4519230769231" customWidth="1"/>
-    <col min="6" max="12" width="17.6346153846154" customWidth="1"/>
+    <col min="1" max="1" width="10.6363636363636"/>
+    <col min="2" max="2" width="25.9090909090909" customWidth="1"/>
+    <col min="3" max="4" width="14.6363636363636" customWidth="1"/>
+    <col min="5" max="5" width="14.4545454545455" customWidth="1"/>
+    <col min="6" max="12" width="17.6363636363636" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -1102,28 +1102,28 @@
       <c r="E2" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="1">
-        <v>46124</v>
+      <c r="A3" s="3">
+        <v>46113</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
@@ -1151,7 +1151,7 @@
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="1"/>
+      <c r="A44" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1164,7 +1164,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1176,7 +1176,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
